--- a/it23839410_test_automation/Assignment 1 - Test cases.xlsx
+++ b/it23839410_test_automation/Assignment 1 - Test cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Naveen\Desktop\itpm\test_automation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Naveen\Desktop\New folder\it23839410_ITPM_assigment1\it23839410_test_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE105E4-B81F-45E0-9C85-A7A4D37C9E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93099BEE-37E5-4A81-8B42-B32C51712127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="2724" windowWidth="17280" windowHeight="9960" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="157">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -501,6 +501,9 @@
   </si>
   <si>
     <t>කඩේට ගිහින් බඩු ටික අරන් ටග්ගලා එන්න.</t>
+  </si>
+  <si>
+    <t>ඊයේ බෝඩිමට ගෙනාපු බඩු වල ගාන කියද?</t>
   </si>
 </sst>
 </file>
@@ -606,21 +609,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -932,24 +935,24 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="str">
+      <c r="A2" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0001</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="5" t="str">
         <f>IF(LEN(C2)&lt;=30,"S",IF(LEN(C2)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -978,24 +981,24 @@
       <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="str">
+      <c r="A6" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0002</v>
       </c>
-      <c r="B6" s="2" t="str">
+      <c r="B6" s="5" t="str">
         <f>IF(LEN(C6)&lt;=30,"S",IF(LEN(C6)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="E6" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1024,24 +1027,24 @@
       <c r="F9" s="4"/>
     </row>
     <row r="10" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="str">
+      <c r="A10" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0003</v>
       </c>
-      <c r="B10" s="2" t="str">
+      <c r="B10" s="5" t="str">
         <f>IF(LEN(C10)&lt;=30,"S",IF(LEN(C10)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1070,24 +1073,24 @@
       <c r="F13" s="4"/>
     </row>
     <row r="14" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="str">
+      <c r="A14" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0004</v>
       </c>
-      <c r="B14" s="2" t="str">
+      <c r="B14" s="5" t="str">
         <f>IF(LEN(C14)&lt;=30,"S",IF(LEN(C14)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1116,24 +1119,24 @@
       <c r="F17" s="4"/>
     </row>
     <row r="18" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="str">
+      <c r="A18" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0005</v>
       </c>
-      <c r="B18" s="2" t="str">
+      <c r="B18" s="5" t="str">
         <f>IF(LEN(C18)&lt;=30,"S",IF(LEN(C18)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1162,24 +1165,24 @@
       <c r="F21" s="4"/>
     </row>
     <row r="22" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="str">
+      <c r="A22" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0006</v>
       </c>
-      <c r="B22" s="2" t="str">
+      <c r="B22" s="5" t="str">
         <f>IF(LEN(C22)&lt;=30,"S",IF(LEN(C22)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1208,24 +1211,24 @@
       <c r="F25" s="4"/>
     </row>
     <row r="26" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="str">
+      <c r="A26" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0007</v>
       </c>
-      <c r="B26" s="2" t="str">
+      <c r="B26" s="5" t="str">
         <f>IF(LEN(C26)&lt;=30,"S",IF(LEN(C26)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1254,24 +1257,24 @@
       <c r="F29" s="4"/>
     </row>
     <row r="30" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="6" t="str">
+      <c r="A30" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0008</v>
       </c>
-      <c r="B30" s="2" t="str">
+      <c r="B30" s="5" t="str">
         <f>IF(LEN(C30)&lt;=30,"S",IF(LEN(C30)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1300,24 +1303,24 @@
       <c r="F33" s="4"/>
     </row>
     <row r="34" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="str">
+      <c r="A34" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0009</v>
       </c>
-      <c r="B34" s="2" t="str">
+      <c r="B34" s="5" t="str">
         <f>IF(LEN(C34)&lt;=30,"S",IF(LEN(C34)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1346,24 +1349,24 @@
       <c r="F37" s="4"/>
     </row>
     <row r="38" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="6" t="str">
+      <c r="A38" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0010</v>
       </c>
-      <c r="B38" s="2" t="str">
+      <c r="B38" s="5" t="str">
         <f>IF(LEN(C38)&lt;=30,"S",IF(LEN(C38)&lt;=299,"M","L"))</f>
         <v>S</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1392,24 +1395,24 @@
       <c r="F41" s="4"/>
     </row>
     <row r="42" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="str">
+      <c r="A42" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0011</v>
       </c>
-      <c r="B42" s="2" t="str">
+      <c r="B42" s="5" t="str">
         <f>IF(LEN(C42)&lt;=30,"S",IF(LEN(C42)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="F42" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1438,24 +1441,24 @@
       <c r="F45" s="4"/>
     </row>
     <row r="46" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="str">
+      <c r="A46" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0012</v>
       </c>
-      <c r="B46" s="2" t="str">
+      <c r="B46" s="5" t="str">
         <f>IF(LEN(C46)&lt;=30,"S",IF(LEN(C46)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E46" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="F46" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1484,24 +1487,24 @@
       <c r="F49" s="4"/>
     </row>
     <row r="50" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="6" t="str">
+      <c r="A50" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0013</v>
       </c>
-      <c r="B50" s="2" t="str">
+      <c r="B50" s="5" t="str">
         <f>IF(LEN(C50)&lt;=30,"S",IF(LEN(C50)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="D50" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E50" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="F50" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1530,24 +1533,24 @@
       <c r="F53" s="4"/>
     </row>
     <row r="54" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="6" t="str">
+      <c r="A54" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0014</v>
       </c>
-      <c r="B54" s="2" t="str">
+      <c r="B54" s="5" t="str">
         <f>IF(LEN(C54)&lt;=30,"S",IF(LEN(C54)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D54" s="7" t="s">
+      <c r="D54" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="E54" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="F54" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1576,24 +1579,24 @@
       <c r="F57" s="4"/>
     </row>
     <row r="58" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="6" t="str">
+      <c r="A58" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0015</v>
       </c>
-      <c r="B58" s="2" t="str">
+      <c r="B58" s="5" t="str">
         <f>IF(LEN(C58)&lt;=30,"S",IF(LEN(C58)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="D58" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E58" s="8" t="s">
+      <c r="E58" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="F58" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1622,24 +1625,24 @@
       <c r="F61" s="4"/>
     </row>
     <row r="62" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="6" t="str">
+      <c r="A62" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0016</v>
       </c>
-      <c r="B62" s="2" t="str">
+      <c r="B62" s="5" t="str">
         <f>IF(LEN(C62)&lt;=30,"S",IF(LEN(C62)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C62" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D62" s="7" t="s">
+      <c r="D62" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="E62" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F62" s="2" t="s">
+      <c r="F62" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1668,24 +1671,24 @@
       <c r="F65" s="4"/>
     </row>
     <row r="66" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="6" t="str">
+      <c r="A66" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0017</v>
       </c>
-      <c r="B66" s="2" t="str">
+      <c r="B66" s="5" t="str">
         <f>IF(LEN(C66)&lt;=30,"S",IF(LEN(C66)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="C66" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="D66" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E66" s="8" t="s">
+      <c r="E66" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F66" s="2" t="s">
+      <c r="F66" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1714,24 +1717,24 @@
       <c r="F69" s="4"/>
     </row>
     <row r="70" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="6" t="str">
+      <c r="A70" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0018</v>
       </c>
-      <c r="B70" s="2" t="str">
+      <c r="B70" s="5" t="str">
         <f>IF(LEN(C70)&lt;=30,"S",IF(LEN(C70)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C70" s="5" t="s">
+      <c r="C70" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D70" s="7" t="s">
+      <c r="D70" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="E70" s="8" t="s">
+      <c r="E70" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F70" s="2" t="s">
+      <c r="F70" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1760,24 +1763,24 @@
       <c r="F73" s="4"/>
     </row>
     <row r="74" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="6" t="str">
+      <c r="A74" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0019</v>
       </c>
-      <c r="B74" s="2" t="str">
+      <c r="B74" s="5" t="str">
         <f>IF(LEN(C74)&lt;=30,"S",IF(LEN(C74)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="C74" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D74" s="7" t="s">
+      <c r="D74" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E74" s="8" t="s">
+      <c r="E74" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="F74" s="2" t="s">
+      <c r="F74" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1806,24 +1809,24 @@
       <c r="F77" s="4"/>
     </row>
     <row r="78" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="6" t="str">
+      <c r="A78" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0020</v>
       </c>
-      <c r="B78" s="2" t="str">
+      <c r="B78" s="5" t="str">
         <f>IF(LEN(C78)&lt;=30,"S",IF(LEN(C78)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C78" s="5" t="s">
+      <c r="C78" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D78" s="7" t="s">
+      <c r="D78" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="E78" s="8" t="s">
+      <c r="E78" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F78" s="2" t="s">
+      <c r="F78" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1852,24 +1855,24 @@
       <c r="F81" s="4"/>
     </row>
     <row r="82" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="6" t="str">
+      <c r="A82" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0021</v>
       </c>
-      <c r="B82" s="2" t="str">
+      <c r="B82" s="5" t="str">
         <f>IF(LEN(C82)&lt;=30,"S",IF(LEN(C82)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C82" s="5" t="s">
+      <c r="C82" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D82" s="7" t="s">
+      <c r="D82" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E82" s="8" t="s">
+      <c r="E82" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F82" s="2" t="s">
+      <c r="F82" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1898,24 +1901,24 @@
       <c r="F85" s="4"/>
     </row>
     <row r="86" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="6" t="str">
+      <c r="A86" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0022</v>
       </c>
-      <c r="B86" s="2" t="str">
+      <c r="B86" s="5" t="str">
         <f>IF(LEN(C86)&lt;=30,"S",IF(LEN(C86)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C86" s="5" t="s">
+      <c r="C86" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D86" s="7" t="s">
+      <c r="D86" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="E86" s="8" t="s">
+      <c r="E86" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F86" s="2" t="s">
+      <c r="F86" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1944,24 +1947,24 @@
       <c r="F89" s="4"/>
     </row>
     <row r="90" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="6" t="str">
+      <c r="A90" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0023</v>
       </c>
-      <c r="B90" s="2" t="str">
+      <c r="B90" s="5" t="str">
         <f>IF(LEN(C90)&lt;=30,"S",IF(LEN(C90)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C90" s="5" t="s">
+      <c r="C90" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D90" s="7" t="s">
+      <c r="D90" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E90" s="8" t="s">
+      <c r="E90" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="F90" s="2" t="s">
+      <c r="F90" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1990,24 +1993,24 @@
       <c r="F93" s="4"/>
     </row>
     <row r="94" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="6" t="str">
+      <c r="A94" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0024</v>
       </c>
-      <c r="B94" s="2" t="str">
+      <c r="B94" s="5" t="str">
         <f>IF(LEN(C94)&lt;=30,"S",IF(LEN(C94)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C94" s="5" t="s">
+      <c r="C94" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D94" s="7" t="s">
+      <c r="D94" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E94" s="8" t="s">
+      <c r="E94" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F94" s="2" t="s">
+      <c r="F94" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2036,24 +2039,24 @@
       <c r="F97" s="4"/>
     </row>
     <row r="98" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="6" t="str">
+      <c r="A98" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0025</v>
       </c>
-      <c r="B98" s="2" t="str">
+      <c r="B98" s="5" t="str">
         <f>IF(LEN(C98)&lt;=30,"S",IF(LEN(C98)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C98" s="5" t="s">
+      <c r="C98" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D98" s="7" t="s">
+      <c r="D98" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E98" s="8" t="s">
+      <c r="E98" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F98" s="2" t="s">
+      <c r="F98" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2082,24 +2085,24 @@
       <c r="F101" s="4"/>
     </row>
     <row r="102" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="6" t="str">
+      <c r="A102" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0026</v>
       </c>
-      <c r="B102" s="2" t="str">
+      <c r="B102" s="5" t="str">
         <f>IF(LEN(C102)&lt;=30,"S",IF(LEN(C102)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C102" s="5" t="s">
+      <c r="C102" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D102" s="7" t="s">
+      <c r="D102" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E102" s="8" t="s">
+      <c r="E102" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="F102" s="2" t="s">
+      <c r="F102" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2128,24 +2131,24 @@
       <c r="F105" s="4"/>
     </row>
     <row r="106" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="6" t="str">
+      <c r="A106" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0027</v>
       </c>
-      <c r="B106" s="2" t="str">
+      <c r="B106" s="5" t="str">
         <f>IF(LEN(C106)&lt;=30,"S",IF(LEN(C106)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C106" s="5" t="s">
+      <c r="C106" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D106" s="7" t="s">
+      <c r="D106" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="E106" s="8" t="s">
+      <c r="E106" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F106" s="2" t="s">
+      <c r="F106" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2174,24 +2177,24 @@
       <c r="F109" s="4"/>
     </row>
     <row r="110" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="6" t="str">
+      <c r="A110" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0028</v>
       </c>
-      <c r="B110" s="2" t="str">
+      <c r="B110" s="5" t="str">
         <f>IF(LEN(C110)&lt;=30,"S",IF(LEN(C110)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C110" s="5" t="s">
+      <c r="C110" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D110" s="7" t="s">
+      <c r="D110" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="E110" s="8" t="s">
+      <c r="E110" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="F110" s="2" t="s">
+      <c r="F110" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2220,24 +2223,24 @@
       <c r="F113" s="4"/>
     </row>
     <row r="114" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="6" t="str">
+      <c r="A114" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0029</v>
       </c>
-      <c r="B114" s="2" t="str">
+      <c r="B114" s="5" t="str">
         <f>IF(LEN(C114)&lt;=30,"S",IF(LEN(C114)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C114" s="5" t="s">
+      <c r="C114" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D114" s="7" t="s">
+      <c r="D114" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="E114" s="8" t="s">
+      <c r="E114" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="F114" s="2" t="s">
+      <c r="F114" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2266,24 +2269,24 @@
       <c r="F117" s="4"/>
     </row>
     <row r="118" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="6" t="str">
+      <c r="A118" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0030</v>
       </c>
-      <c r="B118" s="2" t="str">
+      <c r="B118" s="5" t="str">
         <f>IF(LEN(C118)&lt;=30,"S",IF(LEN(C118)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C118" s="5" t="s">
+      <c r="C118" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D118" s="7" t="s">
+      <c r="D118" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="E118" s="8" t="s">
+      <c r="E118" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="F118" s="2" t="s">
+      <c r="F118" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2312,24 +2315,24 @@
       <c r="F121" s="4"/>
     </row>
     <row r="122" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="6" t="str">
+      <c r="A122" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0031</v>
       </c>
-      <c r="B122" s="2" t="str">
+      <c r="B122" s="5" t="str">
         <f>IF(LEN(C122)&lt;=30,"S",IF(LEN(C122)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C122" s="5" t="s">
+      <c r="C122" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D122" s="7" t="s">
+      <c r="D122" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E122" s="8" t="s">
+      <c r="E122" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F122" s="2" t="s">
+      <c r="F122" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2358,24 +2361,24 @@
       <c r="F125" s="4"/>
     </row>
     <row r="126" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="6" t="str">
+      <c r="A126" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0032</v>
       </c>
-      <c r="B126" s="2" t="str">
+      <c r="B126" s="5" t="str">
         <f>IF(LEN(C126)&lt;=30,"S",IF(LEN(C126)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C126" s="5" t="s">
+      <c r="C126" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D126" s="7" t="s">
+      <c r="D126" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E126" s="8" t="s">
+      <c r="E126" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F126" s="2" t="s">
+      <c r="F126" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2404,24 +2407,24 @@
       <c r="F129" s="4"/>
     </row>
     <row r="130" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="6" t="str">
+      <c r="A130" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0033</v>
       </c>
-      <c r="B130" s="2" t="str">
+      <c r="B130" s="5" t="str">
         <f>IF(LEN(C130)&lt;=30,"S",IF(LEN(C130)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C130" s="5" t="s">
+      <c r="C130" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D130" s="7" t="s">
+      <c r="D130" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="E130" s="8" t="s">
+      <c r="E130" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="F130" s="2" t="s">
+      <c r="F130" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2450,24 +2453,24 @@
       <c r="F133" s="4"/>
     </row>
     <row r="134" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="6" t="str">
+      <c r="A134" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0034</v>
       </c>
-      <c r="B134" s="2" t="str">
+      <c r="B134" s="5" t="str">
         <f>IF(LEN(C134)&lt;=30,"S",IF(LEN(C134)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C134" s="5" t="s">
+      <c r="C134" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D134" s="7" t="s">
+      <c r="D134" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="E134" s="8" t="s">
+      <c r="E134" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="F134" s="2" t="s">
+      <c r="F134" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2496,24 +2499,24 @@
       <c r="F137" s="4"/>
     </row>
     <row r="138" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="6" t="str">
+      <c r="A138" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0035</v>
       </c>
-      <c r="B138" s="2" t="str">
+      <c r="B138" s="5" t="str">
         <f>IF(LEN(C138)&lt;=30,"S",IF(LEN(C138)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C138" s="5" t="s">
+      <c r="C138" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D138" s="7" t="s">
+      <c r="D138" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="E138" s="8" t="s">
+      <c r="E138" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="F138" s="2" t="s">
+      <c r="F138" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2542,24 +2545,24 @@
       <c r="F141" s="4"/>
     </row>
     <row r="142" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="6" t="str">
+      <c r="A142" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0036</v>
       </c>
-      <c r="B142" s="2" t="str">
+      <c r="B142" s="5" t="str">
         <f>IF(LEN(C142)&lt;=30,"S",IF(LEN(C142)&lt;=299,"M","L"))</f>
         <v>S</v>
       </c>
-      <c r="C142" s="5" t="s">
+      <c r="C142" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D142" s="7" t="s">
+      <c r="D142" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="E142" s="8" t="s">
+      <c r="E142" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="F142" s="2" t="s">
+      <c r="F142" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2588,24 +2591,24 @@
       <c r="F145" s="4"/>
     </row>
     <row r="146" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="6" t="str">
+      <c r="A146" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0037</v>
       </c>
-      <c r="B146" s="2" t="str">
+      <c r="B146" s="5" t="str">
         <f>IF(LEN(C146)&lt;=30,"S",IF(LEN(C146)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C146" s="5" t="s">
+      <c r="C146" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D146" s="7" t="s">
+      <c r="D146" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="E146" s="8" t="s">
+      <c r="E146" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="F146" s="2" t="s">
+      <c r="F146" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2634,24 +2637,24 @@
       <c r="F149" s="4"/>
     </row>
     <row r="150" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="6" t="str">
+      <c r="A150" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0038</v>
       </c>
-      <c r="B150" s="2" t="str">
+      <c r="B150" s="5" t="str">
         <f>IF(LEN(C150)&lt;=30,"S",IF(LEN(C150)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C150" s="5" t="s">
+      <c r="C150" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D150" s="7" t="s">
+      <c r="D150" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="E150" s="8" t="s">
+      <c r="E150" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="F150" s="2" t="s">
+      <c r="F150" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2680,24 +2683,24 @@
       <c r="F153" s="4"/>
     </row>
     <row r="154" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="6" t="str">
+      <c r="A154" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0039</v>
       </c>
-      <c r="B154" s="2" t="str">
+      <c r="B154" s="5" t="str">
         <f>IF(LEN(C154)&lt;=30,"S",IF(LEN(C154)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C154" s="5" t="s">
+      <c r="C154" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D154" s="7" t="s">
+      <c r="D154" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="E154" s="8" t="s">
+      <c r="E154" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="F154" s="2" t="s">
+      <c r="F154" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2726,24 +2729,24 @@
       <c r="F157" s="4"/>
     </row>
     <row r="158" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="6" t="str">
+      <c r="A158" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0040</v>
       </c>
-      <c r="B158" s="2" t="str">
+      <c r="B158" s="5" t="str">
         <f>IF(LEN(C158)&lt;=30,"S",IF(LEN(C158)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C158" s="5" t="s">
+      <c r="C158" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D158" s="7" t="s">
+      <c r="D158" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="E158" s="8" t="s">
+      <c r="E158" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="F158" s="2" t="s">
+      <c r="F158" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2772,24 +2775,24 @@
       <c r="F161" s="4"/>
     </row>
     <row r="162" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="6" t="str">
+      <c r="A162" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0041</v>
       </c>
-      <c r="B162" s="2" t="str">
+      <c r="B162" s="5" t="str">
         <f>IF(LEN(C162)&lt;=30,"S",IF(LEN(C162)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C162" s="5" t="s">
+      <c r="C162" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D162" s="7" t="s">
+      <c r="D162" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="E162" s="8" t="s">
+      <c r="E162" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="F162" s="2" t="s">
+      <c r="F162" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2818,24 +2821,24 @@
       <c r="F165" s="4"/>
     </row>
     <row r="166" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="6" t="str">
+      <c r="A166" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0042</v>
       </c>
-      <c r="B166" s="2" t="str">
+      <c r="B166" s="5" t="str">
         <f>IF(LEN(C166)&lt;=30,"S",IF(LEN(C166)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C166" s="5" t="s">
+      <c r="C166" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D166" s="7" t="s">
+      <c r="D166" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="E166" s="8" t="s">
+      <c r="E166" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="F166" s="2" t="s">
+      <c r="F166" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2864,24 +2867,24 @@
       <c r="F169" s="4"/>
     </row>
     <row r="170" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="6" t="str">
+      <c r="A170" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0043</v>
       </c>
-      <c r="B170" s="2" t="str">
+      <c r="B170" s="5" t="str">
         <f>IF(LEN(C170)&lt;=30,"S",IF(LEN(C170)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C170" s="5" t="s">
+      <c r="C170" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D170" s="7" t="s">
+      <c r="D170" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="E170" s="8" t="s">
+      <c r="E170" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="F170" s="2" t="s">
+      <c r="F170" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2910,24 +2913,24 @@
       <c r="F173" s="4"/>
     </row>
     <row r="174" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="6" t="str">
+      <c r="A174" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0044</v>
       </c>
-      <c r="B174" s="2" t="str">
+      <c r="B174" s="5" t="str">
         <f>IF(LEN(C174)&lt;=30,"S",IF(LEN(C174)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C174" s="5" t="s">
+      <c r="C174" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D174" s="7" t="s">
+      <c r="D174" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="E174" s="8" t="s">
+      <c r="E174" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="F174" s="2" t="s">
+      <c r="F174" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2956,24 +2959,24 @@
       <c r="F177" s="4"/>
     </row>
     <row r="178" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="6" t="str">
+      <c r="A178" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0045</v>
       </c>
-      <c r="B178" s="2" t="str">
+      <c r="B178" s="5" t="str">
         <f>IF(LEN(C178)&lt;=30,"S",IF(LEN(C178)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C178" s="5" t="s">
+      <c r="C178" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D178" s="7" t="s">
+      <c r="D178" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="E178" s="8" t="s">
+      <c r="E178" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="F178" s="2" t="s">
+      <c r="F178" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3002,24 +3005,24 @@
       <c r="F181" s="4"/>
     </row>
     <row r="182" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="6" t="str">
+      <c r="A182" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0046</v>
       </c>
-      <c r="B182" s="2" t="str">
+      <c r="B182" s="5" t="str">
         <f>IF(LEN(C182)&lt;=30,"S",IF(LEN(C182)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C182" s="5" t="s">
+      <c r="C182" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D182" s="7" t="s">
+      <c r="D182" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="E182" s="8" t="s">
+      <c r="E182" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="F182" s="2" t="s">
+      <c r="F182" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3048,24 +3051,24 @@
       <c r="F185" s="4"/>
     </row>
     <row r="186" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="6" t="str">
+      <c r="A186" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0047</v>
       </c>
-      <c r="B186" s="2" t="str">
+      <c r="B186" s="5" t="str">
         <f>IF(LEN(C186)&lt;=30,"S",IF(LEN(C186)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C186" s="5" t="s">
+      <c r="C186" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D186" s="7" t="s">
+      <c r="D186" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="E186" s="8" t="s">
+      <c r="E186" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="F186" s="2" t="s">
+      <c r="F186" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3094,24 +3097,24 @@
       <c r="F189" s="4"/>
     </row>
     <row r="190" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="6" t="str">
+      <c r="A190" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0048</v>
       </c>
-      <c r="B190" s="2" t="str">
+      <c r="B190" s="5" t="str">
         <f>IF(LEN(C190)&lt;=30,"S",IF(LEN(C190)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C190" s="5" t="s">
+      <c r="C190" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D190" s="7" t="s">
+      <c r="D190" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="E190" s="8" t="s">
+      <c r="E190" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="F190" s="2" t="s">
+      <c r="F190" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3140,24 +3143,24 @@
       <c r="F193" s="4"/>
     </row>
     <row r="194" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="6" t="str">
+      <c r="A194" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0049</v>
       </c>
-      <c r="B194" s="2" t="str">
+      <c r="B194" s="5" t="str">
         <f>IF(LEN(C194)&lt;=30,"S",IF(LEN(C194)&lt;=299,"M","L"))</f>
         <v>M</v>
       </c>
-      <c r="C194" s="5" t="s">
+      <c r="C194" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D194" s="7" t="s">
+      <c r="D194" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="E194" s="8" t="s">
+      <c r="E194" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="F194" s="2" t="s">
+      <c r="F194" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3186,24 +3189,24 @@
       <c r="F197" s="4"/>
     </row>
     <row r="198" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="6" t="str">
+      <c r="A198" s="7" t="str">
         <f>"Neg_"&amp;TEXT(INT((ROW()-2)/4)+1,"0000")</f>
         <v>Neg_0050</v>
       </c>
-      <c r="B198" s="2" t="str">
+      <c r="B198" s="5" t="str">
         <f>IF(LEN(C198)&lt;=30,"S",IF(LEN(C198)&lt;=299,"M","L"))</f>
         <v>L</v>
       </c>
-      <c r="C198" s="5" t="s">
+      <c r="C198" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D198" s="7" t="s">
+      <c r="D198" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="E198" s="8" t="s">
+      <c r="E198" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="F198" s="2" t="s">
+      <c r="F198" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3233,22 +3236,266 @@
     </row>
   </sheetData>
   <mergeCells count="300">
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="B66:B69"/>
-    <mergeCell ref="C154:C157"/>
-    <mergeCell ref="C98:C101"/>
-    <mergeCell ref="E14:E17"/>
-    <mergeCell ref="A166:A169"/>
-    <mergeCell ref="E102:E105"/>
-    <mergeCell ref="B50:B53"/>
-    <mergeCell ref="A162:A165"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A118:A121"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="C18:C21"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="D22:D25"/>
-    <mergeCell ref="E18:E21"/>
+    <mergeCell ref="C6:C9"/>
+    <mergeCell ref="C62:C65"/>
+    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="A198:A201"/>
+    <mergeCell ref="F194:F197"/>
+    <mergeCell ref="C198:C201"/>
+    <mergeCell ref="D122:D125"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="F122:F125"/>
+    <mergeCell ref="D162:D165"/>
+    <mergeCell ref="C130:C133"/>
+    <mergeCell ref="A126:A129"/>
+    <mergeCell ref="C182:C185"/>
+    <mergeCell ref="A142:A145"/>
+    <mergeCell ref="E182:E185"/>
+    <mergeCell ref="C110:C113"/>
+    <mergeCell ref="F106:F109"/>
+    <mergeCell ref="F186:F189"/>
+    <mergeCell ref="A190:A193"/>
+    <mergeCell ref="C150:C153"/>
+    <mergeCell ref="C190:C193"/>
+    <mergeCell ref="B114:B117"/>
+    <mergeCell ref="D114:D117"/>
+    <mergeCell ref="B154:B157"/>
+    <mergeCell ref="C174:C177"/>
+    <mergeCell ref="F170:F173"/>
+    <mergeCell ref="B138:B141"/>
+    <mergeCell ref="D6:D9"/>
+    <mergeCell ref="C26:C29"/>
+    <mergeCell ref="D190:D193"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="E82:E85"/>
+    <mergeCell ref="F6:F9"/>
+    <mergeCell ref="D86:D89"/>
+    <mergeCell ref="A138:A141"/>
+    <mergeCell ref="F86:F89"/>
+    <mergeCell ref="F142:F145"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="B62:B65"/>
+    <mergeCell ref="E10:E13"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B70:B73"/>
+    <mergeCell ref="D70:D73"/>
+    <mergeCell ref="E98:E101"/>
+    <mergeCell ref="F70:F73"/>
+    <mergeCell ref="E34:E37"/>
+    <mergeCell ref="B182:B185"/>
+    <mergeCell ref="D134:D137"/>
+    <mergeCell ref="F134:F137"/>
+    <mergeCell ref="E62:E65"/>
+    <mergeCell ref="E22:E25"/>
+    <mergeCell ref="C194:C197"/>
+    <mergeCell ref="C38:C41"/>
+    <mergeCell ref="D58:D61"/>
+    <mergeCell ref="F58:F61"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A122:A125"/>
+    <mergeCell ref="C122:C125"/>
+    <mergeCell ref="C78:C81"/>
+    <mergeCell ref="D42:D45"/>
+    <mergeCell ref="A186:A189"/>
+    <mergeCell ref="C186:C189"/>
+    <mergeCell ref="D94:D97"/>
+    <mergeCell ref="E142:E145"/>
+    <mergeCell ref="E194:E197"/>
+    <mergeCell ref="B150:B153"/>
+    <mergeCell ref="A114:A117"/>
+    <mergeCell ref="A170:A173"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="F78:F81"/>
+    <mergeCell ref="C170:C173"/>
+    <mergeCell ref="F118:F121"/>
+    <mergeCell ref="F158:F161"/>
+    <mergeCell ref="B190:B193"/>
+    <mergeCell ref="D194:D197"/>
+    <mergeCell ref="B178:B181"/>
+    <mergeCell ref="E86:E89"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B74:B77"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="F38:F41"/>
+    <mergeCell ref="F50:F53"/>
+    <mergeCell ref="E162:E165"/>
+    <mergeCell ref="D130:D133"/>
+    <mergeCell ref="F130:F133"/>
+    <mergeCell ref="B162:B165"/>
+    <mergeCell ref="A134:A137"/>
+    <mergeCell ref="D74:D77"/>
+    <mergeCell ref="E134:E137"/>
+    <mergeCell ref="D138:D141"/>
+    <mergeCell ref="F54:F57"/>
+    <mergeCell ref="C158:C161"/>
+    <mergeCell ref="F26:F29"/>
+    <mergeCell ref="F154:F157"/>
+    <mergeCell ref="A158:A161"/>
+    <mergeCell ref="C118:C121"/>
+    <mergeCell ref="D186:D189"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="C50:C53"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="F138:F141"/>
+    <mergeCell ref="C142:C145"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="E118:E121"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="D66:D69"/>
+    <mergeCell ref="D106:D109"/>
+    <mergeCell ref="F66:F69"/>
+    <mergeCell ref="B146:B149"/>
+    <mergeCell ref="D18:D21"/>
+    <mergeCell ref="D146:D149"/>
+    <mergeCell ref="E166:E169"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="B198:B201"/>
+    <mergeCell ref="D14:D17"/>
+    <mergeCell ref="A106:A109"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="B174:B177"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="B126:B129"/>
+    <mergeCell ref="D182:D185"/>
+    <mergeCell ref="D38:D41"/>
+    <mergeCell ref="F182:F185"/>
+    <mergeCell ref="A130:A133"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="E106:E109"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="D110:D113"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="E146:E149"/>
+    <mergeCell ref="F166:F169"/>
+    <mergeCell ref="E198:E201"/>
+    <mergeCell ref="C74:C77"/>
+    <mergeCell ref="A110:A113"/>
+    <mergeCell ref="F162:F165"/>
+    <mergeCell ref="C126:C129"/>
+    <mergeCell ref="F190:F193"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="C138:C141"/>
+    <mergeCell ref="E54:E57"/>
+    <mergeCell ref="D30:D33"/>
+    <mergeCell ref="C178:C181"/>
+    <mergeCell ref="E178:E181"/>
+    <mergeCell ref="D62:D65"/>
+    <mergeCell ref="D118:D121"/>
+    <mergeCell ref="F62:F65"/>
+    <mergeCell ref="B94:B97"/>
+    <mergeCell ref="C166:C169"/>
+    <mergeCell ref="E126:E129"/>
+    <mergeCell ref="C58:C61"/>
+    <mergeCell ref="E58:E61"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="E138:E141"/>
+    <mergeCell ref="E190:E193"/>
+    <mergeCell ref="D158:D161"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="F114:F117"/>
+    <mergeCell ref="D154:D157"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="E122:E125"/>
+    <mergeCell ref="F18:F21"/>
+    <mergeCell ref="E78:E81"/>
+    <mergeCell ref="B170:B173"/>
+    <mergeCell ref="A174:A177"/>
+    <mergeCell ref="D170:D173"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="E6:E9"/>
+    <mergeCell ref="C134:C137"/>
+    <mergeCell ref="F22:F25"/>
+    <mergeCell ref="A154:A157"/>
+    <mergeCell ref="E30:E33"/>
+    <mergeCell ref="C114:C117"/>
+    <mergeCell ref="E170:E173"/>
+    <mergeCell ref="E114:E117"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="C70:C73"/>
+    <mergeCell ref="F102:F105"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="B194:B197"/>
+    <mergeCell ref="D10:D13"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="D50:D53"/>
+    <mergeCell ref="F10:F13"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="F146:F149"/>
+    <mergeCell ref="B122:B125"/>
+    <mergeCell ref="E150:E153"/>
+    <mergeCell ref="D178:D181"/>
+    <mergeCell ref="D34:D37"/>
+    <mergeCell ref="F178:F181"/>
+    <mergeCell ref="C42:C45"/>
+    <mergeCell ref="A182:A185"/>
+    <mergeCell ref="F34:F37"/>
+    <mergeCell ref="F74:F77"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="E42:E45"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="B106:B109"/>
+    <mergeCell ref="E186:E189"/>
+    <mergeCell ref="A194:A197"/>
+    <mergeCell ref="E70:E73"/>
+    <mergeCell ref="C106:C109"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="E110:E113"/>
+    <mergeCell ref="B158:B161"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="B186:B189"/>
+    <mergeCell ref="C82:C85"/>
+    <mergeCell ref="D102:D105"/>
+    <mergeCell ref="B142:B145"/>
+    <mergeCell ref="E174:E177"/>
+    <mergeCell ref="D142:D145"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A150:A153"/>
+    <mergeCell ref="E26:E29"/>
+    <mergeCell ref="D98:D101"/>
+    <mergeCell ref="C66:C69"/>
+    <mergeCell ref="A102:A105"/>
+    <mergeCell ref="E66:E69"/>
+    <mergeCell ref="C102:C105"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="D26:D29"/>
+    <mergeCell ref="D198:D201"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="A146:A149"/>
+    <mergeCell ref="F198:F201"/>
+    <mergeCell ref="C146:C149"/>
+    <mergeCell ref="D174:D177"/>
+    <mergeCell ref="A178:A181"/>
+    <mergeCell ref="F174:F177"/>
+    <mergeCell ref="D126:D129"/>
+    <mergeCell ref="C94:C97"/>
+    <mergeCell ref="F126:F129"/>
+    <mergeCell ref="D166:D169"/>
+    <mergeCell ref="E94:E97"/>
+    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="F110:F113"/>
+    <mergeCell ref="D150:D153"/>
+    <mergeCell ref="F150:F153"/>
+    <mergeCell ref="E158:E161"/>
+    <mergeCell ref="B166:B169"/>
+    <mergeCell ref="B118:B121"/>
+    <mergeCell ref="F94:F97"/>
+    <mergeCell ref="E154:E157"/>
+    <mergeCell ref="F98:F101"/>
+    <mergeCell ref="E130:E133"/>
     <mergeCell ref="F30:F33"/>
     <mergeCell ref="B130:B133"/>
     <mergeCell ref="C162:C165"/>
@@ -3273,266 +3520,22 @@
     <mergeCell ref="D54:D57"/>
     <mergeCell ref="B134:B137"/>
     <mergeCell ref="A66:A69"/>
-    <mergeCell ref="D198:D201"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="A146:A149"/>
-    <mergeCell ref="F198:F201"/>
-    <mergeCell ref="C146:C149"/>
-    <mergeCell ref="D174:D177"/>
-    <mergeCell ref="A178:A181"/>
-    <mergeCell ref="F174:F177"/>
-    <mergeCell ref="D126:D129"/>
-    <mergeCell ref="C94:C97"/>
-    <mergeCell ref="F126:F129"/>
-    <mergeCell ref="D166:D169"/>
-    <mergeCell ref="E94:E97"/>
-    <mergeCell ref="E90:E93"/>
-    <mergeCell ref="F110:F113"/>
-    <mergeCell ref="D150:D153"/>
-    <mergeCell ref="F150:F153"/>
-    <mergeCell ref="E158:E161"/>
-    <mergeCell ref="B166:B169"/>
-    <mergeCell ref="B118:B121"/>
-    <mergeCell ref="F94:F97"/>
-    <mergeCell ref="E154:E157"/>
-    <mergeCell ref="F98:F101"/>
-    <mergeCell ref="E130:E133"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="E110:E113"/>
-    <mergeCell ref="B158:B161"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="B186:B189"/>
-    <mergeCell ref="C82:C85"/>
-    <mergeCell ref="D102:D105"/>
-    <mergeCell ref="B142:B145"/>
-    <mergeCell ref="E174:E177"/>
-    <mergeCell ref="D142:D145"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A150:A153"/>
-    <mergeCell ref="E26:E29"/>
-    <mergeCell ref="D98:D101"/>
-    <mergeCell ref="C66:C69"/>
-    <mergeCell ref="A102:A105"/>
-    <mergeCell ref="E66:E69"/>
-    <mergeCell ref="C102:C105"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="D26:D29"/>
-    <mergeCell ref="B194:B197"/>
-    <mergeCell ref="D10:D13"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="D50:D53"/>
-    <mergeCell ref="F10:F13"/>
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="F146:F149"/>
-    <mergeCell ref="B122:B125"/>
-    <mergeCell ref="E150:E153"/>
-    <mergeCell ref="D178:D181"/>
-    <mergeCell ref="D34:D37"/>
-    <mergeCell ref="F178:F181"/>
-    <mergeCell ref="C42:C45"/>
-    <mergeCell ref="A182:A185"/>
-    <mergeCell ref="F34:F37"/>
-    <mergeCell ref="F74:F77"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="E42:E45"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="B106:B109"/>
-    <mergeCell ref="E186:E189"/>
-    <mergeCell ref="A194:A197"/>
-    <mergeCell ref="E70:E73"/>
-    <mergeCell ref="C106:C109"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="D2:D5"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="C22:C25"/>
-    <mergeCell ref="E122:E125"/>
-    <mergeCell ref="F18:F21"/>
-    <mergeCell ref="E78:E81"/>
-    <mergeCell ref="B170:B173"/>
-    <mergeCell ref="A174:A177"/>
-    <mergeCell ref="D170:D173"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="E6:E9"/>
-    <mergeCell ref="C134:C137"/>
-    <mergeCell ref="F22:F25"/>
-    <mergeCell ref="A154:A157"/>
-    <mergeCell ref="E30:E33"/>
-    <mergeCell ref="C114:C117"/>
-    <mergeCell ref="E170:E173"/>
-    <mergeCell ref="E114:E117"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="C70:C73"/>
-    <mergeCell ref="F102:F105"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="F190:F193"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="C138:C141"/>
-    <mergeCell ref="E54:E57"/>
-    <mergeCell ref="D30:D33"/>
-    <mergeCell ref="C178:C181"/>
-    <mergeCell ref="E178:E181"/>
-    <mergeCell ref="D62:D65"/>
-    <mergeCell ref="D118:D121"/>
-    <mergeCell ref="F62:F65"/>
-    <mergeCell ref="B94:B97"/>
-    <mergeCell ref="C166:C169"/>
-    <mergeCell ref="E126:E129"/>
-    <mergeCell ref="C58:C61"/>
-    <mergeCell ref="E58:E61"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="B102:B105"/>
-    <mergeCell ref="E138:E141"/>
-    <mergeCell ref="E190:E193"/>
-    <mergeCell ref="D158:D161"/>
-    <mergeCell ref="B98:B101"/>
-    <mergeCell ref="F114:F117"/>
-    <mergeCell ref="D154:D157"/>
-    <mergeCell ref="B198:B201"/>
-    <mergeCell ref="D14:D17"/>
-    <mergeCell ref="A106:A109"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="B174:B177"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="B126:B129"/>
-    <mergeCell ref="D182:D185"/>
-    <mergeCell ref="D38:D41"/>
-    <mergeCell ref="F182:F185"/>
-    <mergeCell ref="A130:A133"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="E106:E109"/>
-    <mergeCell ref="B54:B57"/>
-    <mergeCell ref="D110:D113"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="E146:E149"/>
-    <mergeCell ref="F166:F169"/>
-    <mergeCell ref="E198:E201"/>
-    <mergeCell ref="C74:C77"/>
-    <mergeCell ref="A110:A113"/>
-    <mergeCell ref="F162:F165"/>
-    <mergeCell ref="C126:C129"/>
-    <mergeCell ref="F26:F29"/>
-    <mergeCell ref="F154:F157"/>
-    <mergeCell ref="A158:A161"/>
-    <mergeCell ref="C118:C121"/>
-    <mergeCell ref="D186:D189"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="C50:C53"/>
-    <mergeCell ref="B82:B85"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="F138:F141"/>
-    <mergeCell ref="C142:C145"/>
-    <mergeCell ref="F90:F93"/>
-    <mergeCell ref="E118:E121"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="D66:D69"/>
-    <mergeCell ref="D106:D109"/>
-    <mergeCell ref="F66:F69"/>
-    <mergeCell ref="B146:B149"/>
-    <mergeCell ref="D18:D21"/>
-    <mergeCell ref="D146:D149"/>
-    <mergeCell ref="E166:E169"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="B178:B181"/>
-    <mergeCell ref="E86:E89"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B74:B77"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="F38:F41"/>
-    <mergeCell ref="F50:F53"/>
-    <mergeCell ref="E162:E165"/>
-    <mergeCell ref="D130:D133"/>
-    <mergeCell ref="F130:F133"/>
-    <mergeCell ref="B162:B165"/>
-    <mergeCell ref="A134:A137"/>
-    <mergeCell ref="D74:D77"/>
-    <mergeCell ref="E134:E137"/>
-    <mergeCell ref="D138:D141"/>
-    <mergeCell ref="F54:F57"/>
-    <mergeCell ref="C158:C161"/>
-    <mergeCell ref="C194:C197"/>
-    <mergeCell ref="C38:C41"/>
-    <mergeCell ref="D58:D61"/>
-    <mergeCell ref="F58:F61"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A122:A125"/>
-    <mergeCell ref="C122:C125"/>
-    <mergeCell ref="C78:C81"/>
-    <mergeCell ref="D42:D45"/>
-    <mergeCell ref="A186:A189"/>
-    <mergeCell ref="C186:C189"/>
-    <mergeCell ref="D94:D97"/>
-    <mergeCell ref="E142:E145"/>
-    <mergeCell ref="E194:E197"/>
-    <mergeCell ref="B150:B153"/>
-    <mergeCell ref="A114:A117"/>
-    <mergeCell ref="A170:A173"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="F78:F81"/>
-    <mergeCell ref="C170:C173"/>
-    <mergeCell ref="F118:F121"/>
-    <mergeCell ref="F158:F161"/>
-    <mergeCell ref="B190:B193"/>
-    <mergeCell ref="D194:D197"/>
-    <mergeCell ref="D6:D9"/>
-    <mergeCell ref="C26:C29"/>
-    <mergeCell ref="D190:D193"/>
-    <mergeCell ref="B86:B89"/>
-    <mergeCell ref="E82:E85"/>
-    <mergeCell ref="F6:F9"/>
-    <mergeCell ref="D86:D89"/>
-    <mergeCell ref="A138:A141"/>
-    <mergeCell ref="F86:F89"/>
-    <mergeCell ref="F142:F145"/>
-    <mergeCell ref="C10:C13"/>
-    <mergeCell ref="B62:B65"/>
-    <mergeCell ref="E10:E13"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B70:B73"/>
-    <mergeCell ref="D70:D73"/>
-    <mergeCell ref="E98:E101"/>
-    <mergeCell ref="F70:F73"/>
-    <mergeCell ref="E34:E37"/>
-    <mergeCell ref="B182:B185"/>
-    <mergeCell ref="D134:D137"/>
-    <mergeCell ref="F134:F137"/>
-    <mergeCell ref="E62:E65"/>
-    <mergeCell ref="E22:E25"/>
-    <mergeCell ref="A198:A201"/>
-    <mergeCell ref="F194:F197"/>
-    <mergeCell ref="C198:C201"/>
-    <mergeCell ref="D122:D125"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="F122:F125"/>
-    <mergeCell ref="D162:D165"/>
-    <mergeCell ref="C130:C133"/>
-    <mergeCell ref="A126:A129"/>
-    <mergeCell ref="C182:C185"/>
-    <mergeCell ref="A142:A145"/>
-    <mergeCell ref="E182:E185"/>
-    <mergeCell ref="C110:C113"/>
-    <mergeCell ref="F106:F109"/>
-    <mergeCell ref="F186:F189"/>
-    <mergeCell ref="A190:A193"/>
-    <mergeCell ref="C150:C153"/>
-    <mergeCell ref="C190:C193"/>
-    <mergeCell ref="B114:B117"/>
-    <mergeCell ref="D114:D117"/>
-    <mergeCell ref="B154:B157"/>
-    <mergeCell ref="C174:C177"/>
-    <mergeCell ref="F170:F173"/>
-    <mergeCell ref="B138:B141"/>
-    <mergeCell ref="C6:C9"/>
-    <mergeCell ref="C62:C65"/>
-    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="B66:B69"/>
+    <mergeCell ref="C154:C157"/>
+    <mergeCell ref="C98:C101"/>
+    <mergeCell ref="E14:E17"/>
+    <mergeCell ref="A166:A169"/>
+    <mergeCell ref="E102:E105"/>
+    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="A162:A165"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A118:A121"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="C18:C21"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="D22:D25"/>
+    <mergeCell ref="E18:E21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
